--- a/docs/03_tests/部署削除BBテスト.xlsx
+++ b/docs/03_tests/部署削除BBテスト.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\削除\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5720615B-9CDB-4924-92FA-9522A7F39949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB3CF21-DF91-4AAD-8D89-566F8E200198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{75EC8E91-D408-484C-993F-76DDAF482B23}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{75EC8E91-D408-484C-993F-76DDAF482B23}"/>
   </bookViews>
   <sheets>
     <sheet name="条件" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
   <si>
     <t>条件</t>
     <rPh sb="0" eb="2">
@@ -400,6 +400,52 @@
   </si>
   <si>
     <t>1-3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2-2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リロードする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>値を保持したままConfirmページから遷移しない</t>
+    <rPh sb="0" eb="1">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホジ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>リロードをする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>続行をクリック</t>
+    <rPh sb="0" eb="2">
+      <t>ゾッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Comlete画面のまま</t>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3-3</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -891,6 +937,154 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>88901</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>184483</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D73FB3AF-98C6-45E0-D2FF-C89838FFD718}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="838201" y="7239000"/>
+          <a:ext cx="2711449" cy="1175083"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1041400</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1447800</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="矢印: 下 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A86670E5-30A6-3BEF-30C4-288B4E51C29C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1790700" y="8496300"/>
+          <a:ext cx="406400" cy="717550"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>654050</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>184151</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>793476</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF49DEF9-3010-1CE3-F14A-12D211FA0EB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="654050" y="9328151"/>
+          <a:ext cx="3092176" cy="958850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -976,6 +1170,50 @@
         <a:xfrm>
           <a:off x="835025" y="3435350"/>
           <a:ext cx="2643527" cy="1755775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>787401</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>50801</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>579671</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>203201</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55739499-483A-E86A-2A72-5167B058D47F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="787401" y="5537201"/>
+          <a:ext cx="2668820" cy="1066800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1464,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BB74C5D-10D3-4321-B7E3-9D3151A3523B}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="9.83203125" style="3" customWidth="1"/>
@@ -1522,6 +1760,17 @@
         <v>39</v>
       </c>
     </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+    </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3" t="s">
         <v>16</v>
@@ -1535,6 +1784,16 @@
     <row r="25" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C39" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1546,7 +1805,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27160D7A-4369-459E-8673-FCBD45B91E39}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="2" customWidth="1"/>
@@ -1594,6 +1853,17 @@
         <v>19</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+    </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>24</v>
@@ -1602,6 +1872,11 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/docs/03_tests/部署削除BBテスト.xlsx
+++ b/docs/03_tests/部署削除BBテスト.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\削除\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB3CF21-DF91-4AAD-8D89-566F8E200198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86B661B-F48A-48CD-8D12-79A880B3D1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{75EC8E91-D408-484C-993F-76DDAF482B23}"/>
+    <workbookView xWindow="3400" yWindow="1990" windowWidth="14400" windowHeight="7280" activeTab="3" xr2:uid="{75EC8E91-D408-484C-993F-76DDAF482B23}"/>
   </bookViews>
   <sheets>
     <sheet name="条件" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
   <si>
     <t>条件</t>
     <rPh sb="0" eb="2">
@@ -281,25 +281,6 @@
     <t>所属社員がいる</t>
     <rPh sb="0" eb="4">
       <t>ショゾクシャイン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Confirm画面に遷移し、総務部と表示される</t>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>センイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ソウム</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ブ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -438,14 +419,27 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Comlete画面のまま</t>
+    <t>3-3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Confirm画面に遷移し、「この部署には現在 1 名の社員が所属しています。
+削除を実行すると、該当の社員は自動的に「未所属」になります。」「総務部」と表示される</t>
     <rPh sb="7" eb="9">
       <t>ガメン</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3-3</t>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>ソウム</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -492,7 +486,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -516,6 +510,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -626,23 +623,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>781050</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>115474</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1800225</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>162340</xdr:rowOff>
+      <xdr:colOff>1181100</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>112201</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7666B671-0A20-1AA7-9135-E4831BAD86FB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{323FD39E-98EB-1FF8-0252-DEFA2A96ABDA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -658,8 +655,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="781050" y="5830474"/>
-          <a:ext cx="3343275" cy="1189866"/>
+          <a:off x="793750" y="6400801"/>
+          <a:ext cx="2711450" cy="1483800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -807,50 +804,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>228599</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>470911</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>142874</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{563D7883-D949-9EA6-7CE5-8B6D3AC4EC90}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="752475" y="5714999"/>
-          <a:ext cx="2671186" cy="1285875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>809625</xdr:colOff>
       <xdr:row>25</xdr:row>
@@ -876,7 +829,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -920,7 +873,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -964,7 +917,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1068,7 +1021,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1077,6 +1030,50 @@
         <a:xfrm>
           <a:off x="654050" y="9328151"/>
           <a:ext cx="3092176" cy="958850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>190499</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>18143</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>480785</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>212277</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46D69379-B5D7-663E-BE0D-D15B653609FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="943428" y="5461000"/>
+          <a:ext cx="2494643" cy="1328063"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1180,23 +1177,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>787401</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>103910</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>50801</xdr:rowOff>
+      <xdr:rowOff>57728</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>579671</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>203201</xdr:rowOff>
+      <xdr:colOff>246302</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>196274</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55739499-483A-E86A-2A72-5167B058D47F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29480047-77E3-8CCA-E5AB-2E6D3671C11D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1212,8 +1209,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="787401" y="5537201"/>
-          <a:ext cx="2668820" cy="1066800"/>
+          <a:off x="912092" y="5599546"/>
+          <a:ext cx="2197483" cy="1293092"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1563,10 +1560,10 @@
         <v>46169</v>
       </c>
       <c r="F2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1574,7 +1571,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1599,7 +1596,7 @@
     <col min="1" max="1" width="10.4140625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.08203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="49.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63.08203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -1646,7 +1643,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:4" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -1656,8 +1653,8 @@
       <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="D6" t="s">
-        <v>34</v>
+      <c r="D6" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1685,12 +1682,12 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1740,35 +1737,35 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
         <v>44</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>45</v>
-      </c>
-      <c r="D7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1778,22 +1775,22 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="C39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1855,13 +1852,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
         <v>47</v>
       </c>
-      <c r="B6" t="s">
-        <v>48</v>
-      </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1876,7 +1873,7 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
